--- a/RL/results_dnn_film_b.xlsx
+++ b/RL/results_dnn_film_b.xlsx
@@ -605,7 +605,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>334.7</v>
+        <v>130.5</v>
       </c>
       <c r="V2" t="n">
         <v>166.05</v>
@@ -636,49 +636,49 @@
         <v>41.77</v>
       </c>
       <c r="H3" t="n">
-        <v>38258</v>
+        <v>36069</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>38258</v>
+        <v>36069</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>279.3</v>
+        <v>187.2</v>
       </c>
       <c r="V3" t="n">
-        <v>198.23</v>
+        <v>197.03</v>
       </c>
     </row>
     <row r="4">
@@ -745,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>67</v>
+        <v>65.5</v>
       </c>
       <c r="V4" t="n">
         <v>166.05</v>
@@ -776,49 +776,49 @@
         <v>41.77</v>
       </c>
       <c r="H5" t="n">
-        <v>38258</v>
+        <v>36069</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>38258</v>
+        <v>36069</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>255.5</v>
+        <v>208.2</v>
       </c>
       <c r="V5" t="n">
-        <v>198.23</v>
+        <v>197.03</v>
       </c>
     </row>
     <row r="6">
@@ -885,7 +885,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>87.40000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="V6" t="n">
         <v>226.05</v>
@@ -916,49 +916,49 @@
         <v>41.77</v>
       </c>
       <c r="H7" t="n">
-        <v>38258</v>
+        <v>36069</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>38258</v>
+        <v>36069</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>297.2</v>
+        <v>183.6</v>
       </c>
       <c r="V7" t="n">
-        <v>258.23</v>
+        <v>257.03</v>
       </c>
     </row>
     <row r="8">
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>91.7</v>
+        <v>48</v>
       </c>
       <c r="V8" t="n">
         <v>226.05</v>
@@ -1095,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>257.6</v>
+        <v>173.5</v>
       </c>
       <c r="V9" t="n">
         <v>258.23</v>
@@ -1126,49 +1126,49 @@
         <v>73.95</v>
       </c>
       <c r="H10" t="n">
-        <v>5008</v>
+        <v>4064</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>73.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5008</v>
+        <v>4064</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>73.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>86.90000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="V10" t="n">
-        <v>999926.05</v>
+        <v>999924.85</v>
       </c>
     </row>
     <row r="11">
@@ -1235,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>227.2</v>
+        <v>188.8</v>
       </c>
       <c r="V11" t="n">
         <v>999958.23</v>
@@ -1305,7 +1305,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>74.8</v>
+        <v>318.6</v>
       </c>
       <c r="V12" t="n">
         <v>999926.05</v>
@@ -1375,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>243.6</v>
+        <v>191.9</v>
       </c>
       <c r="V13" t="n">
         <v>999958.23</v>
@@ -1445,22 +1445,22 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>9.98</v>
+        <v>12.84</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.98</v>
+        <v>12.84</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>182.14</v>
+        <v>181.54</v>
       </c>
     </row>
     <row r="3">
@@ -1471,22 +1471,22 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>11.44</v>
+        <v>12.88</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>11.44</v>
+        <v>12.88</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>242.14</v>
+        <v>241.84</v>
       </c>
     </row>
     <row r="4">
@@ -1497,22 +1497,22 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>7.93</v>
+        <v>12.64</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>7.93</v>
+        <v>12.64</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>999942.14</v>
+        <v>999941.84</v>
       </c>
     </row>
   </sheetData>

--- a/RL/results_dnn_film_b.xlsx
+++ b/RL/results_dnn_film_b.xlsx
@@ -566,7 +566,7 @@
         <v>73.95</v>
       </c>
       <c r="H2" t="n">
-        <v>4009</v>
+        <v>3010</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -575,13 +575,13 @@
         <v>73.95</v>
       </c>
       <c r="K2" t="n">
-        <v>19.95</v>
+        <v>39.9</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4009</v>
+        <v>3010</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -590,22 +590,22 @@
         <v>73.95</v>
       </c>
       <c r="P2" t="n">
-        <v>19.95</v>
+        <v>39.9</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>130.5</v>
+        <v>539.5</v>
       </c>
       <c r="V2" t="n">
         <v>166.05</v>
@@ -636,49 +636,49 @@
         <v>41.77</v>
       </c>
       <c r="H3" t="n">
-        <v>36069</v>
+        <v>29262</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>42.97</v>
+        <v>41.77</v>
       </c>
       <c r="K3" t="n">
-        <v>5.72</v>
+        <v>23.51</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>36069</v>
+        <v>29262</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>42.97</v>
+        <v>41.77</v>
       </c>
       <c r="P3" t="n">
-        <v>5.72</v>
+        <v>23.51</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>187.2</v>
+        <v>2188.3</v>
       </c>
       <c r="V3" t="n">
-        <v>197.03</v>
+        <v>198.23</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>73.95</v>
       </c>
       <c r="H4" t="n">
-        <v>4009</v>
+        <v>3010</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -715,13 +715,13 @@
         <v>73.95</v>
       </c>
       <c r="K4" t="n">
-        <v>19.95</v>
+        <v>39.9</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4009</v>
+        <v>3010</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -730,22 +730,22 @@
         <v>73.95</v>
       </c>
       <c r="P4" t="n">
-        <v>19.95</v>
+        <v>39.9</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>65.5</v>
+        <v>407.4</v>
       </c>
       <c r="V4" t="n">
         <v>166.05</v>
@@ -776,49 +776,49 @@
         <v>41.77</v>
       </c>
       <c r="H5" t="n">
-        <v>36069</v>
+        <v>29262</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>42.97</v>
+        <v>41.77</v>
       </c>
       <c r="K5" t="n">
-        <v>5.72</v>
+        <v>23.51</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>36069</v>
+        <v>29262</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>42.97</v>
+        <v>41.77</v>
       </c>
       <c r="P5" t="n">
-        <v>5.72</v>
+        <v>23.51</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>208.2</v>
+        <v>2266.7</v>
       </c>
       <c r="V5" t="n">
-        <v>197.03</v>
+        <v>198.23</v>
       </c>
     </row>
     <row r="6">
@@ -846,7 +846,7 @@
         <v>73.95</v>
       </c>
       <c r="H6" t="n">
-        <v>4009</v>
+        <v>5008</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -855,13 +855,13 @@
         <v>73.95</v>
       </c>
       <c r="K6" t="n">
-        <v>19.95</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4009</v>
+        <v>5008</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -870,22 +870,22 @@
         <v>73.95</v>
       </c>
       <c r="P6" t="n">
-        <v>19.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>52.5</v>
+        <v>250.3</v>
       </c>
       <c r="V6" t="n">
         <v>226.05</v>
@@ -916,49 +916,49 @@
         <v>41.77</v>
       </c>
       <c r="H7" t="n">
-        <v>36069</v>
+        <v>29262</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>42.97</v>
+        <v>41.77</v>
       </c>
       <c r="K7" t="n">
-        <v>5.72</v>
+        <v>23.51</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>36069</v>
+        <v>29262</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>42.97</v>
+        <v>41.77</v>
       </c>
       <c r="P7" t="n">
-        <v>5.72</v>
+        <v>23.51</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>183.6</v>
+        <v>2316.7</v>
       </c>
       <c r="V7" t="n">
-        <v>257.03</v>
+        <v>258.23</v>
       </c>
     </row>
     <row r="8">
@@ -986,7 +986,7 @@
         <v>73.95</v>
       </c>
       <c r="H8" t="n">
-        <v>4009</v>
+        <v>3010</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>73.95</v>
       </c>
       <c r="K8" t="n">
-        <v>19.95</v>
+        <v>39.9</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4009</v>
+        <v>3010</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1010,22 +1010,22 @@
         <v>73.95</v>
       </c>
       <c r="P8" t="n">
-        <v>19.95</v>
+        <v>39.9</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
       <c r="R8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>48</v>
+        <v>414.5</v>
       </c>
       <c r="V8" t="n">
         <v>226.05</v>
@@ -1056,7 +1056,7 @@
         <v>41.77</v>
       </c>
       <c r="H9" t="n">
-        <v>36009</v>
+        <v>22515</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1065,13 +1065,13 @@
         <v>41.77</v>
       </c>
       <c r="K9" t="n">
-        <v>5.88</v>
+        <v>41.15</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>36009</v>
+        <v>22515</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1080,22 +1080,22 @@
         <v>41.77</v>
       </c>
       <c r="P9" t="n">
-        <v>5.88</v>
+        <v>41.15</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
       <c r="R9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>173.5</v>
+        <v>3376.8</v>
       </c>
       <c r="V9" t="n">
         <v>258.23</v>
@@ -1126,49 +1126,49 @@
         <v>73.95</v>
       </c>
       <c r="H10" t="n">
-        <v>4064</v>
+        <v>5008</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>75.15000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="K10" t="n">
-        <v>18.85</v>
+        <v>0</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4064</v>
+        <v>5008</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>75.15000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="P10" t="n">
-        <v>18.85</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
       <c r="R10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>50.6</v>
+        <v>327.9</v>
       </c>
       <c r="V10" t="n">
-        <v>999924.85</v>
+        <v>999926.05</v>
       </c>
     </row>
     <row r="11">
@@ -1196,7 +1196,7 @@
         <v>41.77</v>
       </c>
       <c r="H11" t="n">
-        <v>36009</v>
+        <v>22515</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1205,13 +1205,13 @@
         <v>41.77</v>
       </c>
       <c r="K11" t="n">
-        <v>5.88</v>
+        <v>41.15</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>36009</v>
+        <v>22515</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1220,22 +1220,22 @@
         <v>41.77</v>
       </c>
       <c r="P11" t="n">
-        <v>5.88</v>
+        <v>41.15</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
       <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U11" t="n">
-        <v>188.8</v>
+        <v>3426.3</v>
       </c>
       <c r="V11" t="n">
         <v>999958.23</v>
@@ -1266,7 +1266,7 @@
         <v>73.95</v>
       </c>
       <c r="H12" t="n">
-        <v>4009</v>
+        <v>3010</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1275,13 +1275,13 @@
         <v>73.95</v>
       </c>
       <c r="K12" t="n">
-        <v>19.95</v>
+        <v>39.9</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4009</v>
+        <v>3010</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1290,22 +1290,22 @@
         <v>73.95</v>
       </c>
       <c r="P12" t="n">
-        <v>19.95</v>
+        <v>39.9</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
       <c r="R12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>318.6</v>
+        <v>434.2</v>
       </c>
       <c r="V12" t="n">
         <v>999926.05</v>
@@ -1336,7 +1336,7 @@
         <v>41.77</v>
       </c>
       <c r="H13" t="n">
-        <v>36009</v>
+        <v>22515</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>41.77</v>
       </c>
       <c r="K13" t="n">
-        <v>5.88</v>
+        <v>41.15</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>36009</v>
+        <v>22515</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1360,22 +1360,22 @@
         <v>41.77</v>
       </c>
       <c r="P13" t="n">
-        <v>5.88</v>
+        <v>41.15</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
       <c r="R13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
-        <v>191.9</v>
+        <v>3368</v>
       </c>
       <c r="V13" t="n">
         <v>999958.23</v>
@@ -1445,22 +1445,22 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>12.84</v>
+        <v>31.7</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>12.84</v>
+        <v>31.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>181.54</v>
+        <v>182.14</v>
       </c>
     </row>
     <row r="3">
@@ -1471,22 +1471,22 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>12.88</v>
+        <v>26.14</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>12.88</v>
+        <v>26.14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>241.84</v>
+        <v>242.14</v>
       </c>
     </row>
     <row r="4">
@@ -1497,22 +1497,22 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>12.64</v>
+        <v>30.55</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12.64</v>
+        <v>30.55</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>999941.84</v>
+        <v>999942.14</v>
       </c>
     </row>
   </sheetData>
